--- a/Mantenimiento/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,7 +1302,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1444,7 +1349,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1496,7 +1396,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1548,7 +1443,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1600,7 +1490,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1652,7 +1537,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1704,7 +1584,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1732,11 +1612,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1756,7 +1631,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1783,11 +1658,6 @@
       </c>
       <c r="K26" t="n">
         <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>018 OKINAWA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.9502</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.08179</v>
-      </c>
-      <c r="I2" t="n">
-        <v>362</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.9502</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.08179</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>2005 LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.01125</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.0792</v>
-      </c>
-      <c r="I3" t="n">
-        <v>538</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.01125</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.0792</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.00754</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.07722</v>
-      </c>
-      <c r="I4" t="n">
-        <v>753</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.00754</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.07722</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>2025 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.945275</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.0746</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1438</v>
-      </c>
-      <c r="J5" t="n">
-        <v>67</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.945275</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.0746</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.9897</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.0778</v>
-      </c>
-      <c r="I6" t="n">
-        <v>400</v>
-      </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.9897</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.0778</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>2071 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.99395</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.07665</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J7" t="n">
-        <v>64</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.99395</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.07665</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>2090 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.01</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.0735</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1082</v>
-      </c>
-      <c r="J8" t="n">
-        <v>57</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.01</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.0735</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.98945</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.07302</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1482</v>
-      </c>
-      <c r="J9" t="n">
-        <v>68</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.98945</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.07302</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>2096 PERU JAPON</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.9802</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.06829999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1004</v>
-      </c>
-      <c r="J10" t="n">
-        <v>45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.9802</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.0683</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>3080 PERU - CANADA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.9558</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.07467</v>
-      </c>
-      <c r="I11" t="n">
-        <v>966</v>
-      </c>
-      <c r="J11" t="n">
-        <v>47</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.9558</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.07467</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>3091</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.94144</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.076683</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J12" t="n">
-        <v>61</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.94144</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.076683</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>3095 PERU KAWACHI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.92235</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.07501999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>992</v>
-      </c>
-      <c r="J13" t="n">
-        <v>53</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.92235</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.07502</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>3047</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.94905</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.07250000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>317</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.94905</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.0725</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>PALMAS REALES</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.9933</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.07899999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>638</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.9933</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.079</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>ALFREDO REBAZA ACOSTA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.0032</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.0665</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1316</v>
-      </c>
-      <c r="J16" t="n">
-        <v>68</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.0032</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.0665</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.97452</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.06945</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1003</v>
-      </c>
-      <c r="J17" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.97452</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.06945</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.9734</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.0843</v>
-      </c>
-      <c r="I18" t="n">
-        <v>448</v>
-      </c>
-      <c r="J18" t="n">
-        <v>39</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.9734</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.0843</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.98614</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.07040000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>389</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.98614</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.0704</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>BH SCHOOL</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.97959</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.07473</v>
-      </c>
-      <c r="I20" t="n">
-        <v>664</v>
-      </c>
-      <c r="J20" t="n">
-        <v>38</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.97959</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.07473</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>SAN VICENTE FERRER</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.99345</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.07559999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2523</v>
-      </c>
-      <c r="J21" t="n">
-        <v>111</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.99345</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.0756</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.96696</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.07281</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1519</v>
-      </c>
-      <c r="J22" t="n">
-        <v>54</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.96696</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.07281</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.935869</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.079397</v>
-      </c>
-      <c r="I23" t="n">
-        <v>315</v>
-      </c>
-      <c r="J23" t="n">
-        <v>22</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.935869</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.079397</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.99284</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.06999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>546</v>
-      </c>
-      <c r="J24" t="n">
-        <v>30</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.99284</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.06999</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.951</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.07792000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1403</v>
-      </c>
-      <c r="J25" t="n">
-        <v>60</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.951</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.07792</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1644,20 +1872,30 @@
           <t>MANUEL DUATO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.99665</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.06843000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.99665</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.06843</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
